--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512417_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512417_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2582</v>
+        <v>5.0556</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5919</v>
+        <v>4.0166</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6663</v>
+        <v>1.039</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6787</v>
+        <v>4.392</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4124</v>
+        <v>0.1191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2663</v>
+        <v>4.2729</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7219</v>
+        <v>4.3991</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5243</v>
+        <v>0.0586</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1976</v>
+        <v>4.3405</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0432</v>
+        <v>-0.0071</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1119</v>
+        <v>0.0605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0687</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5795</v>
+        <v>-0.3486</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8943</v>
+        <v>-0.3826</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6852</v>
+        <v>0.0339</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9645</v>
+        <v>4.905</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3948</v>
+        <v>3.6923</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5697</v>
+        <v>1.2127</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3702</v>
+        <v>3.7089</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2886</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0816</v>
+        <v>0.2519</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4379</v>
+        <v>3.7929</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1218</v>
+        <v>3.5941</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3161</v>
+        <v>0.1988</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9323</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1668</v>
+        <v>-0.1371</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7655</v>
+        <v>0.0531</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6145</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6388</v>
+        <v>1.0123</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1474</v>
+        <v>1.1961</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1488</v>
+        <v>0.9117</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0013</v>
+        <v>0.2844</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8324</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8324</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6783</v>
+        <v>4.5347</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6294</v>
+        <v>2.0489</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0489</v>
+        <v>2.4858</v>
       </c>
       <c r="G4" t="n">
-        <v>4.377</v>
+        <v>2.4047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1281</v>
+        <v>1.3415</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2489</v>
+        <v>1.0632</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3415</v>
+        <v>1.5198</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0448</v>
+        <v>1.2017</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2967</v>
+        <v>0.318</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0355</v>
+        <v>0.885</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0833</v>
+        <v>0.1398</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0477</v>
+        <v>0.7452</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0242</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0242</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.723</v>
+        <v>0.6766</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7121</v>
+        <v>0.6954</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0108</v>
+        <v>-0.0188</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5157</v>
+        <v>3.856</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3891</v>
+        <v>3.5475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1266</v>
+        <v>0.3085</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0249</v>
+        <v>2.8567</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2217</v>
+        <v>0.6524</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8032</v>
+        <v>2.2042</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7564</v>
+        <v>2.2864</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5565</v>
+        <v>0.3944</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.892</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2684</v>
+        <v>0.5703</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3348</v>
+        <v>0.258</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6032</v>
+        <v>0.3122</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4293</v>
+        <v>-0.0129</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1728</v>
+        <v>0.0708</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2566</v>
+        <v>-0.0838</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9385</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4841</v>
+        <v>1.1902</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4227</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1656</v>
+        <v>3.7596</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9704</v>
+        <v>3.6811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1952</v>
+        <v>0.0785</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8512</v>
+        <v>4.0383</v>
       </c>
       <c r="H6" t="n">
-        <v>0.655</v>
+        <v>2.2331</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1962</v>
+        <v>1.8052</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2483</v>
+        <v>3.8041</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3766</v>
+        <v>2.5879</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8717</v>
+        <v>1.2161</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6029</v>
+        <v>0.2343</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2784</v>
+        <v>-0.3548</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3245</v>
+        <v>0.5891</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7099</v>
+        <v>0.6606</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4585</v>
+        <v>0.3875</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2514</v>
+        <v>0.2731</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9393</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>0.5019</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1806</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4594</v>
+        <v>3.3889</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5271</v>
+        <v>3.4169</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0281</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3825</v>
+        <v>3.3648</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9782</v>
+        <v>0.9691</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4043</v>
+        <v>2.3958</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2963</v>
+        <v>3.3341</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7278</v>
+        <v>0.75</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5685</v>
+        <v>2.5841</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0862</v>
+        <v>0.0307</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2504</v>
+        <v>0.219</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1642</v>
+        <v>-0.1883</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1392</v>
+        <v>-0.1544</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7693</v>
+        <v>0.0828</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3699</v>
+        <v>-0.2373</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7959</v>
+        <v>2.5075</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2361</v>
+        <v>1.892</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5599</v>
+        <v>0.6155</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3774</v>
+        <v>4.4009</v>
       </c>
       <c r="H8" t="n">
-        <v>1.628</v>
+        <v>1.6401</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7494</v>
+        <v>2.7608</v>
       </c>
       <c r="J8" t="n">
-        <v>3.701</v>
+        <v>3.775</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1825</v>
+        <v>1.2235</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5185</v>
+        <v>2.5516</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6765</v>
+        <v>0.6258</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4455</v>
+        <v>0.4166</v>
       </c>
       <c r="O8" t="n">
-        <v>0.231</v>
+        <v>0.2092</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1476</v>
+        <v>-0.4762</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5728</v>
+        <v>-0.0365</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5748</v>
+        <v>-0.4397</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6867</v>
+        <v>1.7272</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3781</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3086</v>
+        <v>1.2096</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4069</v>
+        <v>1.4096</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7748</v>
+        <v>-0.7711</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1817</v>
+        <v>2.1807</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7711</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.673</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4621</v>
+        <v>1.4709</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6358</v>
+        <v>0.6117</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0838</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7197</v>
+        <v>0.7098</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3347</v>
+        <v>-0.2898</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.393</v>
+        <v>-0.2804</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0583</v>
+        <v>-0.0094</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0632</v>
+        <v>1.129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4038</v>
+        <v>0.7399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6594</v>
+        <v>0.3891</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5674</v>
+        <v>1.621</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6837</v>
+        <v>-2.6505</v>
       </c>
       <c r="I10" t="n">
-        <v>4.251</v>
+        <v>4.2715</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3041</v>
+        <v>1.408</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3208</v>
+        <v>-2.2567</v>
       </c>
       <c r="L10" t="n">
-        <v>3.6249</v>
+        <v>3.6647</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2633</v>
+        <v>0.213</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3628</v>
+        <v>-0.3938</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6261</v>
+        <v>0.6068</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4716</v>
+        <v>0.4958</v>
       </c>
       <c r="T10" t="n">
-        <v>0.124</v>
+        <v>0.3441</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3476</v>
+        <v>0.1516</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5812</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1468</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7281</v>
+        <v>1.5384</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1056</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5714</v>
+        <v>-0.5732</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4658</v>
+        <v>0.4829</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4347</v>
+        <v>-0.3862</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3202</v>
+        <v>-0.2977</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1145</v>
+        <v>-0.0885</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3291</v>
+        <v>0.2959</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2512</v>
+        <v>-0.2755</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5803</v>
+        <v>0.5714</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7241</v>
+        <v>0.8046</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3121</v>
+        <v>0.5259</v>
       </c>
       <c r="U11" t="n">
-        <v>0.412</v>
+        <v>0.2787</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7254</v>
+        <v>-1.0641</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3206</v>
+        <v>-1.7726</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5952</v>
+        <v>0.7085</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1379</v>
+        <v>-1.1501</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2872</v>
+        <v>-0.2961</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8506</v>
+        <v>-0.854</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7966</v>
+        <v>-1.7795</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4821</v>
+        <v>-0.4748</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3145</v>
+        <v>-1.3047</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6587</v>
+        <v>0.6294</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1949</v>
+        <v>0.1787</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.636</v>
+        <v>0.0614</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.524</v>
+        <v>0.0068</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.112</v>
+        <v>0.0546</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.44329999999999</v>
+        <v>30.4652</v>
       </c>
       <c r="E13" t="n">
-        <v>20.0533</v>
+        <v>20.9077</v>
       </c>
       <c r="F13" t="n">
-        <v>10.3903</v>
+        <v>9.557499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>26.7927</v>
+        <v>26.9565</v>
       </c>
       <c r="H13" t="n">
-        <v>5.994899999999999</v>
+        <v>6.121400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>20.7978</v>
+        <v>20.8351</v>
       </c>
       <c r="J13" t="n">
-        <v>22.3472</v>
+        <v>22.9516</v>
       </c>
       <c r="K13" t="n">
-        <v>5.720200000000001</v>
+        <v>6.108</v>
       </c>
       <c r="L13" t="n">
-        <v>16.6271</v>
+        <v>16.8435</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4455</v>
+        <v>4.005</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2747999999999999</v>
+        <v>0.01330000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>4.171</v>
+        <v>3.9916</v>
       </c>
       <c r="P13" t="n">
-        <v>5.121</v>
+        <v>5.0615</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.193700000000002</v>
+        <v>-8.0983</v>
       </c>
       <c r="R13" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6615</v>
+        <v>2.6132</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2223</v>
+        <v>2.3255</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4395000000000001</v>
+        <v>0.2873</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.1321</v>
+        <v>-4.165699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6777</v>
+        <v>3.7283</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.8099</v>
+        <v>-7.893899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0324</v>
+        <v>0.2117</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6997</v>
+        <v>1.9235</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7322</v>
+        <v>-1.7118</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5434</v>
+        <v>0.5379</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2677</v>
+        <v>-0.2763</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8111</v>
+        <v>0.8143</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8962</v>
+        <v>1.908</v>
       </c>
       <c r="K14" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8572</v>
+        <v>1.8685</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3529</v>
+        <v>-1.37</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3068</v>
+        <v>-0.3158</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0461</v>
+        <v>-1.0542</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2965</v>
+        <v>-0.0268</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1965</v>
+        <v>0.0155</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1001</v>
+        <v>-0.0424</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1106</v>
+        <v>-0.3846</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1977</v>
+        <v>0.8724</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3083</v>
+        <v>-1.257</v>
       </c>
       <c r="G15" t="n">
-        <v>0.096</v>
+        <v>0.0693</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0172</v>
+        <v>1.0086</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9213</v>
+        <v>-0.9393</v>
       </c>
       <c r="J15" t="n">
-        <v>1.933</v>
+        <v>1.9562</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8539</v>
+        <v>1.8767</v>
       </c>
       <c r="L15" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.837</v>
+        <v>-1.887</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8367</v>
+        <v>-0.8682</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0003</v>
+        <v>-1.0188</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3144</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0237</v>
+        <v>-0.4275</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2907</v>
+        <v>-0.1798</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3234</v>
+        <v>-2.4126</v>
       </c>
       <c r="E16" t="n">
-        <v>0.297</v>
+        <v>1.019</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6204</v>
+        <v>-3.4315</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.9519</v>
+        <v>-3.7882</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6452</v>
+        <v>-1.0686</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.3067</v>
+        <v>-2.7196</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.1237</v>
+        <v>-0.5478</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2818</v>
+        <v>-0.4195</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1581</v>
+        <v>-0.1283</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8282</v>
+        <v>-3.2404</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3634</v>
+        <v>-0.6491</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.4647</v>
+        <v>-2.5913</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4097</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0382</v>
+        <v>-0.3042</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2644</v>
+        <v>0.1139</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7738</v>
+        <v>-0.4181</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1806</v>
+        <v>2.2872</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1806</v>
+        <v>3.4774</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.2601</v>
+        <v>-3.5814</v>
       </c>
       <c r="E17" t="n">
-        <v>0.401</v>
+        <v>-3.1911</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6611</v>
+        <v>-0.3904</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.8043</v>
+        <v>-4.5132</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0923</v>
+        <v>-1.7787</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.712</v>
+        <v>-2.7344</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6599</v>
+        <v>-3.3017</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5059</v>
+        <v>-1.3447</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.154</v>
+        <v>-1.957</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1443</v>
+        <v>-1.2115</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5863</v>
+        <v>-0.4341</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.558</v>
+        <v>-0.7774</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4339</v>
+        <v>0.4049</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0963</v>
+        <v>0.5268</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3261</v>
+        <v>0.1106</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7702</v>
+        <v>0.4162</v>
       </c>
       <c r="V17" t="n">
-        <v>2.255</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4356</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4233</v>
+        <v>-3.5918</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.0141</v>
+        <v>-1.2664</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4093</v>
+        <v>-2.3255</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.512</v>
+        <v>-5.9967</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7728</v>
+        <v>-2.6486</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7391</v>
+        <v>-3.3481</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.3262</v>
+        <v>-2.0582</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3545</v>
+        <v>-2.2172</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9717</v>
+        <v>0.159</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1857</v>
+        <v>-3.9385</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4183</v>
+        <v>-0.4314</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7674</v>
+        <v>-3.5071</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>1.4172</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.8098</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3121</v>
+        <v>0.6139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3668</v>
+        <v>0.1959</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2375</v>
+        <v>-3.9045</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9127</v>
+        <v>-1.7113</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3248</v>
+        <v>-2.1931</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0045</v>
+        <v>-3.1441</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8221000000000001</v>
+        <v>-1.1047</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.8265</v>
+        <v>-2.0394</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3064</v>
+        <v>-1.3944</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8539</v>
+        <v>-0.4945</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5475</v>
+        <v>-0.8999</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3108</v>
+        <v>-1.7497</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0318</v>
+        <v>-0.6101</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.279</v>
+        <v>-1.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2533</v>
+        <v>0.8098</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0203</v>
+        <v>-0.9751</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1464</v>
+        <v>-0.3169</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1667</v>
+        <v>-0.6582</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7115</v>
+        <v>-4.0226</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3972</v>
+        <v>-2.8025</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3143</v>
+        <v>-1.2201</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1065</v>
+        <v>-1.9971</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0599</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0466</v>
+        <v>-2.8081</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4314</v>
+        <v>0.3643</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5016</v>
+        <v>1.8767</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9298</v>
+        <v>-1.5125</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.675</v>
+        <v>-2.3614</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5583</v>
+        <v>-1.0657</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1167</v>
+        <v>-1.2957</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8194</v>
+        <v>-2.227</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8342</v>
+        <v>0.2015</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9658</v>
+        <v>-0.13</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8683999999999999</v>
+        <v>0.3315</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5903</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4083</v>
+        <v>-4.2591</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6927</v>
+        <v>-2.7632</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7155</v>
+        <v>-1.4959</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1899</v>
+        <v>-2.2285</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8944</v>
+        <v>0.871</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0843</v>
+        <v>-3.0994</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2803</v>
+        <v>0.3187</v>
       </c>
       <c r="K21" t="n">
-        <v>0.923</v>
+        <v>0.9476</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6427</v>
+        <v>-0.6288</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4702</v>
+        <v>-2.5472</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0286</v>
+        <v>-0.0766</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4415</v>
+        <v>-2.4706</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1327</v>
+        <v>0.0424</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9003</v>
+        <v>-0.0452</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2324</v>
+        <v>0.0876</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.9363</v>
+        <v>-7.1361</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.969</v>
+        <v>-1.6381</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.9673</v>
+        <v>-5.498</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.863</v>
+        <v>-5.8959</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8905</v>
+        <v>-1.9349</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.9725</v>
+        <v>-3.961</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.32</v>
+        <v>-1.25</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3007</v>
+        <v>-0.2779</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0193</v>
+        <v>-0.9721</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.543</v>
+        <v>-4.6459</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5898</v>
+        <v>-1.657</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.9531</v>
+        <v>-2.9889</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7251</v>
+        <v>-0.896</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4571</v>
+        <v>-0.2218</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2679</v>
+        <v>-0.6742</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-30.4434</v>
+        <v>-29.081</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.3903</v>
+        <v>-9.557700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.0532</v>
+        <v>-19.5233</v>
       </c>
       <c r="G23" t="n">
-        <v>-26.7927</v>
+        <v>-26.9565</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.9947</v>
+        <v>-6.1212</v>
       </c>
       <c r="I23" t="n">
-        <v>-20.7979</v>
+        <v>-20.835</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.4453</v>
+        <v>-4.004899999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2747</v>
+        <v>-0.01329999999999981</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.170700000000001</v>
+        <v>-3.9916</v>
       </c>
       <c r="M23" t="n">
-        <v>-22.3471</v>
+        <v>-22.9516</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.720000000000001</v>
+        <v>-6.108000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.6268</v>
+        <v>-16.8435</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.1211</v>
+        <v>-5.061400000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R23" t="n">
-        <v>8.193800000000001</v>
+        <v>8.0982</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6618</v>
+        <v>-1.229</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4393999999999997</v>
+        <v>-0.2875</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.2224</v>
+        <v>-0.9415</v>
       </c>
       <c r="V23" t="n">
-        <v>4.1321</v>
+        <v>4.165699999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8098</v>
+        <v>7.893999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.6777</v>
+        <v>-3.7283</v>
       </c>
     </row>
   </sheetData>
